--- a/DataRepo/tests/data/data_submission/animal_sample_good.xlsx
+++ b/DataRepo/tests/data/data_submission/animal_sample_good.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10916"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10628"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-LOCAL/TRACEBASE/tracebase/DataRepo/data/tests/data_submission/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/rleach/PROJECT-local/TRACEBASE/tracebase/DataRepo/tests/data/data_submission/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{93A72E57-DB49-7E43-BC19-500AB1F7FF4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{83357884-A385-5747-877A-30656494FDE9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="14380" yWindow="5220" windowWidth="33060" windowHeight="20340" tabRatio="500" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -476,12 +476,6 @@
     <t>File Format</t>
   </si>
   <si>
-    <t>DataRepo/data/tests/data_submission/accucor1.xlsx</t>
-  </si>
-  <si>
-    <t>DataRepo/data/tests/data_submission/accucor2.xlsx</t>
-  </si>
-  <si>
     <t>accucor</t>
   </si>
   <si>
@@ -489,6 +483,12 @@
   </si>
   <si>
     <t>Default Sequence</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/data_submission/accucor1.xlsx</t>
+  </si>
+  <si>
+    <t>DataRepo/tests/data/data_submission/accucor2.xlsx</t>
   </si>
 </sst>
 </file>
@@ -1013,7 +1013,7 @@
   <sheetData>
     <row r="1" spans="1:30" ht="15.75" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B1" s="3" t="s">
         <v>8</v>
@@ -15874,23 +15874,23 @@
         <v>36</v>
       </c>
       <c r="C1" s="13" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A2" s="12" t="s">
+        <v>40</v>
+      </c>
+      <c r="B2" s="12" t="s">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
+      <c r="A3" s="12" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
+      <c r="B3" s="12" t="s">
         <v>37</v>
-      </c>
-      <c r="B2" s="12" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.15">
-      <c r="A3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B3" s="12" t="s">
-        <v>39</v>
       </c>
     </row>
   </sheetData>
